--- a/data/trans_dic/IP16A06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,08</t>
+          <t>0,0; 26,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,63</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,58</t>
+          <t>0,0; 14,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,74</t>
+          <t>0,0; 13,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,39</t>
+          <t>0,0; 9,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 7,12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,34</t>
+          <t>0,0; 10,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,11</t>
+          <t>0,0; 18,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,2</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,75</t>
+          <t>0,0; 11,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,81</t>
+          <t>0,0; 27,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,71</t>
+          <t>0,0; 15,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,81</t>
+          <t>0,0; 18,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>0,0; 8,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,35</t>
+          <t>0,0; 17,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,95</t>
+          <t>0,0; 18,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,59</t>
+          <t>0,0; 8,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,25</t>
+          <t>0,0; 11,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 19,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,28</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,9</t>
+          <t>0,0; 13,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,33</t>
+          <t>0,0; 24,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,59</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,69</t>
+          <t>0,0; 9,7</t>
         </is>
       </c>
     </row>
@@ -1447,32 +1448,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,67</t>
+          <t>0,0; 11,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,57</t>
+          <t>0,0; 14,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,73</t>
+          <t>0,0; 10,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,67</t>
+          <t>0,0; 13,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,11</t>
+          <t>0,0; 10,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1482,12 +1483,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,14</t>
+          <t>0,0; 7,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,0</t>
+          <t>0,87; 7,29</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,53</t>
+          <t>0,48; 4,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,88</t>
+          <t>0,43; 4,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,91</t>
+          <t>0,84; 5,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,56</t>
+          <t>0,37; 3,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,73</t>
+          <t>0,4; 3,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,64</t>
+          <t>0,91; 3,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,01</t>
+          <t>0,7; 2,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,07</t>
+          <t>0,36; 2,03</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3112</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4758</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3604</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3245</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3983</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3137</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3430</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3658</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2741</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4276</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4573</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3177</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3548</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4027</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3501</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4331</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2994</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2741</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4787</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2696</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3320</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3615</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3472</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3780</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3268</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2872</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4107</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4034</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3610</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3276</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4748</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4075</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>516; 4344</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2947</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>5256</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>600; 5792</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>801; 7718</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3906</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1203; 7641</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>717; 7266</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>592; 5602</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2455; 9969</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2647; 10913</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1113; 6298</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Provincia-trans_dic.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,68</t>
+          <t>0,0; 21,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,96</t>
+          <t>0,0; 21,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,71</t>
+          <t>0,0; 13,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,63</t>
+          <t>0,0; 12,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,13</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,12</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,41</t>
+          <t>0,0; 10,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,42</t>
+          <t>0,0; 18,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,69</t>
+          <t>0,0; 10,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 5,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,33</t>
+          <t>0,0; 27,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,0</t>
+          <t>0,0; 15,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,15</t>
+          <t>0,0; 19,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,15</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,4</t>
+          <t>0,0; 19,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,23</t>
+          <t>0,0; 17,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,36</t>
+          <t>0,0; 10,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,5</t>
+          <t>0,0; 12,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,84</t>
+          <t>0,0; 25,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,63</t>
+          <t>0,0; 13,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,86</t>
+          <t>0,0; 28,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,7</t>
+          <t>0,0; 11,54</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,08</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,37 +1458,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,02</t>
+          <t>0,0; 13,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 7,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,42</t>
+          <t>0,0; 13,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,82</t>
+          <t>0,0; 9,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,22</t>
+          <t>0,0; 6,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,95</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,29</t>
+          <t>0,87; 7,63</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,62</t>
+          <t>0,48; 4,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,13</t>
+          <t>0,44; 4,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,31</t>
+          <t>0,85; 5,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,79</t>
+          <t>0,36; 3,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,78</t>
+          <t>0,39; 3,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,7</t>
+          <t>0,91; 3,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,88</t>
+          <t>0,69; 2,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,03</t>
+          <t>0,36; 2,11</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3112</t>
+          <t>0; 2461</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4758</t>
+          <t>0; 4020</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3604</t>
+          <t>0; 3240</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3245</t>
+          <t>0; 3016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3983</t>
+          <t>0; 3673</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3137</t>
+          <t>0; 3123</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3430</t>
+          <t>0; 3439</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3658</t>
+          <t>0; 3676</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2741</t>
+          <t>0; 2504</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4276</t>
+          <t>0; 3889</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4573</t>
+          <t>0; 3986</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3177</t>
+          <t>0; 3180</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3548</t>
+          <t>0; 3688</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4027</t>
+          <t>0; 4357</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3501</t>
+          <t>0; 3478</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4331</t>
+          <t>0; 4890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2994</t>
+          <t>0; 2890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2741</t>
+          <t>0; 3347</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4787</t>
+          <t>0; 5192</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2696</t>
+          <t>0; 3407</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3320</t>
+          <t>0; 3935</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3615</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3472</t>
+          <t>0; 3922</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3780</t>
+          <t>0; 2931</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3268</t>
+          <t>0; 3887</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2872</t>
+          <t>0; 2718</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,37 +3012,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4107</t>
+          <t>0; 3939</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4034</t>
+          <t>0; 3098</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3610</t>
+          <t>0; 3540</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3276</t>
+          <t>0; 2990</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 4748</t>
+          <t>0; 4059</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4075</t>
+          <t>0; 2996</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>516; 4344</t>
+          <t>519; 4547</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>600; 5792</t>
+          <t>597; 5896</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>801; 7718</t>
+          <t>816; 7603</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 4043</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1203; 7641</t>
+          <t>1217; 7719</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>717; 7266</t>
+          <t>691; 6602</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>592; 5602</t>
+          <t>584; 5067</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2455; 9969</t>
+          <t>2461; 9327</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2647; 10913</t>
+          <t>2626; 11063</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1113; 6298</t>
+          <t>1107; 6564</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,13%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,29%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 27,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,67</t>
+          <t>0,0; 12,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,42</t>
+          <t>0,0; 8,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,05%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 8,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 10,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,63</t>
+          <t>0,0; 11,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,67</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,8%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,64</t>
+          <t>0,0; 17,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,1</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,84%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,21</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,47</t>
+          <t>0,0; 12,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,78</t>
+          <t>0,0; 11,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 20,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 7,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,54</t>
+          <t>0,0; 8,69</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>3,9%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,48</t>
+          <t>0,0; 8,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,45</t>
+          <t>0,0; 10,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,77</t>
+          <t>0,0; 12,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,88</t>
+          <t>0,0; 12,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,17</t>
+          <t>0,0; 7,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 7,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,63</t>
+          <t>0,88; 8,0</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,7</t>
+          <t>0,82; 4,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,07</t>
+          <t>0,36; 3,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,4; 3,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,36</t>
+          <t>0,48; 4,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,45</t>
+          <t>0,43; 3,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,42</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,46</t>
+          <t>0,97; 3,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,92</t>
+          <t>0,7; 3,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,11</t>
+          <t>0,34; 2,07</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2461</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4020</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3083</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4123</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3240</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3016</t>
+          <t>0; 3032</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3673</t>
+          <t>0; 3661</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3123</t>
+          <t>0; 3421</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1971,27 +1971,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>675</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1195</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4191</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3439</t>
+          <t>0; 3057</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3676</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2504</t>
+          <t>0; 3408</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3889</t>
+          <t>0; 4300</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3986</t>
+          <t>0; 4456</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2081,14 +2081,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2134,27 +2134,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3180</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3716</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3688</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4357</t>
+          <t>0; 3951</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3478</t>
+          <t>0; 3497</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2244,27 +2244,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2297,27 +2297,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>593</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1454</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3112</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4890</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2890</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4319</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3347</t>
+          <t>0; 3142</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5192</t>
+          <t>0; 5101</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3384</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3407</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3935</t>
+          <t>0; 3767</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>725</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3421</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2839</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3632</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2931</t>
+          <t>0; 3646</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3887</t>
+          <t>0; 2926</t>
         </is>
       </c>
     </row>
@@ -2901,27 +2901,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>1141</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2718</t>
+          <t>0; 3479</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3677</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3939</t>
+          <t>0; 3061</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3098</t>
+          <t>0; 3286</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3540</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2990</t>
+          <t>0; 3683</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 4059</t>
+          <t>0; 4747</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 2996</t>
+          <t>0; 3659</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>519; 4547</t>
+          <t>523; 4766</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1141</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>597; 5896</t>
+          <t>1184; 7061</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>816; 7603</t>
+          <t>689; 6824</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>589; 5531</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1217; 7719</t>
+          <t>596; 5677</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>691; 6602</t>
+          <t>798; 7263</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>584; 5067</t>
+          <t>0; 3951</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2461; 9327</t>
+          <t>2610; 9806</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2626; 11063</t>
+          <t>2631; 11380</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1107; 6564</t>
+          <t>1048; 6442</t>
         </is>
       </c>
     </row>
